--- a/docs/02_機能毎のテスト/試験項目表_AJAX.xlsx
+++ b/docs/02_機能毎のテスト/試験項目表_AJAX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Git\home\issues\TSF4J5-4861_spring-func\docs\02_機能毎のテスト\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\terasolunaorg_minor\spring-functionaltest\docs\02_機能毎のテスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A964888-19F0-44B8-B025-23CFBB71CD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6407D8CD-2CD0-490B-850F-E286A6928D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="3240" windowWidth="18330" windowHeight="12165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22450" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大中項目" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="87">
   <si>
     <t>機能ID</t>
     <rPh sb="0" eb="2">
@@ -328,10 +328,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Ajaxを使いXML形式のデータを送受信することができることを確認する。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>AJAX0101</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -341,10 +337,6 @@
   </si>
   <si>
     <t>AJAX0103</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>AJAX0104</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -912,15 +904,6 @@
     </rPh>
     <rPh sb="254" eb="256">
       <t>ヘンキャク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">以下のXMLをリクエストすること
-&lt;!DOCTYPE comment [&lt;!ELEMENT comment ANY &gt;&lt;!ENTITY xxe SYSTEM "～～～.txt" &gt;]&gt;&lt;messageBoardForm&gt;&lt;comment&gt;&amp;xxe;Test&lt;/comment&gt;&lt;/messageBoardForm&gt;
-</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -970,34 +953,6 @@
   </si>
   <si>
     <t>【レスポンスデータ】
-Httpステータスコードが "400" で返却されること</t>
-    <rPh sb="32" eb="34">
-      <t>ヘンキャク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>AjaxでフォームのデータをDTD指定ありのXMLデータに変換してからPOSTした場合、リクエストエラーとなることを確認する。</t>
-    <rPh sb="17" eb="19">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>フォームデータをXML形式（DTD指定あり）に変換し、POSTメソッド、Acceptヘッダーにapplication/xml を指定してリクエストする。</t>
-    <rPh sb="17" eb="19">
-      <t>シテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>【レスポンスデータ】
 Controllerの引数に設定された、フォームデータを受け取るためのJavaBeanに、Viewで送信されたフォームデータが設定されていること
 Httpステータスコードが "200" で返却されること
 Content-Type: Content-Type:application/jsonが設定されていること
@@ -1121,57 +1076,6 @@
       <t>ヒキスウ</t>
     </rPh>
     <rPh sb="146" eb="148">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">以下のBean定義を追加する。
-&lt;bean id="xmlMarshaller" class="org.springframework.oxm.jaxb.Jaxb2Marshaller"&gt;
-    &lt;property name="packagesToScan" value="試験パッケージの設定" /&gt;
-&lt;/bean&gt;
-&lt;mvc:annotation-driven&gt;
-    &lt;mvc:message-converters&gt;
-        &lt;bean class="org.springframework.http.converter.xml.MarshallingHttpMessageConverter"&gt;
-            &lt;property name="marshaller" ref="xmlMarshaller" /&gt;
-            &lt;property name="unmarshaller" ref="xmlMarshaller" /&gt;
-&lt;!-- omiited --&gt;
-AjaxでフォームデータをXML形式に変換し送信する
-試験対象のControllerに以下のアノテーションを付与したメソッドを設定する。
-・@PostMapping(value = "任意")
-・@ResponseBody
-メソッドの引数にフォームデータを受け取るためのXmlRootElement アノテーションが付与されたJavaBeanを設定しておく。
-返却するデータを格納するJavaBeanを作成し、
-処理結果を設定する。
-</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>テイギ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="146" eb="148">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="470" eb="472">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="473" eb="475">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="476" eb="478">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="571" eb="573">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="626" eb="628">
       <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -1539,6 +1443,9 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1580,9 +1487,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1959,16 +1863,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.25" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.265625" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" customWidth="1"/>
     <col min="4" max="4" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1976,22 +1880,22 @@
         <v>24</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="43" cm="1">
-        <f t="array" aca="1" ref="C2" ca="1">SUMPRODUCT(IF(LEFT($A$5:$A$65497, 4)=$B$1, N(INDIRECT($A$5:$A$65497 &amp; "!C2")), 0))</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C2" s="29" cm="1">
+        <f t="array" aca="1" ref="C2" ca="1">SUMPRODUCT(IF(LEFT($A$5:$A$65496, 4)=$B$1, N(INDIRECT($A$5:$A$65496 &amp; "!C2")), 0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -2005,13 +1909,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="str">
         <f>IF(B5="","",($B$1&amp;TEXT(IF(B5="","",COUNTA($B$5:B5)),"00")))</f>
         <v>AJAX01</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" s="24" t="str">
         <f>IF(B5="",($B$1&amp;TEXT(IF(B5="",COUNTA($B$5:B5),1),"00")),A5)&amp;IF(B5&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A5&lt;&gt;"",1,RIGHT(#REF!,2)+1),"00"))</f>
@@ -2021,7 +1925,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="str">
         <f>IF(B6="","",($B$1&amp;TEXT(IF(B6="","",COUNTA($B$5:B6)),"00")))</f>
         <v/>
@@ -2035,7 +1939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="str">
         <f>IF(B7="","",($B$1&amp;TEXT(IF(B7="","",COUNTA($B$5:B7)),"00")))</f>
         <v/>
@@ -2049,89 +1953,75 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="22" t="str">
+    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="str">
         <f>IF(B8="","",($B$1&amp;TEXT(IF(B8="","",COUNTA($B$5:B8)),"00")))</f>
-        <v/>
-      </c>
-      <c r="B8" s="20"/>
+        <v>AJAX02</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>67</v>
+      </c>
       <c r="C8" s="24" t="str">
         <f>IF(B8="",($B$1&amp;TEXT(IF(B8="",COUNTA($B$5:B8),1),"00")),A8)&amp;IF(B8&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A8&lt;&gt;"",1,RIGHT(C7,2)+1),"00"))</f>
-        <v>AJAX0104</v>
+        <v>AJAX0201</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="27" x14ac:dyDescent="0.15">
-      <c r="A9" s="25" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="str">
         <f>IF(B9="","",($B$1&amp;TEXT(IF(B9="","",COUNTA($B$5:B9)),"00")))</f>
-        <v>AJAX02</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>69</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B9" s="20"/>
       <c r="C9" s="24" t="str">
         <f>IF(B9="",($B$1&amp;TEXT(IF(B9="",COUNTA($B$5:B9),1),"00")),A9)&amp;IF(B9&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A9&lt;&gt;"",1,RIGHT(C8,2)+1),"00"))</f>
-        <v>AJAX0201</v>
+        <v>AJAX0202</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="str">
         <f>IF(B10="","",($B$1&amp;TEXT(IF(B10="","",COUNTA($B$5:B10)),"00")))</f>
-        <v/>
-      </c>
-      <c r="B10" s="20"/>
+        <v>AJAX03</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="C10" s="24" t="str">
         <f>IF(B10="",($B$1&amp;TEXT(IF(B10="",COUNTA($B$5:B10),1),"00")),A10)&amp;IF(B10&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A10&lt;&gt;"",1,RIGHT(C9,2)+1),"00"))</f>
-        <v>AJAX0202</v>
+        <v>AJAX0301</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="27" x14ac:dyDescent="0.15">
-      <c r="A11" s="22" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="str">
         <f>IF(B11="","",($B$1&amp;TEXT(IF(B11="","",COUNTA($B$5:B11)),"00")))</f>
-        <v>AJAX03</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>70</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="24" t="str">
         <f>IF(B11="",($B$1&amp;TEXT(IF(B11="",COUNTA($B$5:B11),1),"00")),A11)&amp;IF(B11&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A11&lt;&gt;"",1,RIGHT(C10,2)+1),"00"))</f>
-        <v>AJAX0301</v>
+        <v>AJAX0302</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="27" x14ac:dyDescent="0.15">
-      <c r="A12" s="26" t="str">
-        <f>IF(B12="","",($B$1&amp;TEXT(IF(B12="","",COUNTA($B$5:B12)),"00")))</f>
-        <v/>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="24" t="str">
-        <f>IF(B12="",($B$1&amp;TEXT(IF(B12="",COUNTA($B$5:B12),1),"00")),A12)&amp;IF(B12&lt;&gt;"",TEXT(1,"00"),TEXT(IF(A12&lt;&gt;"",1,RIGHT(C11,2)+1),"00"))</f>
-        <v>AJAX0302</v>
-      </c>
-      <c r="D12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A5:B12">
+  <conditionalFormatting sqref="A5:B11">
     <cfRule type="expression" dxfId="3" priority="86">
       <formula>A5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="A12" location="PRPT01!A1" display="PRPT01!A1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A11" location="PRPT01!A1" display="PRPT01!A1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A7" location="PRPT01!A1" display="PRPT01!A1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2147,24 +2037,24 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="7" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="7" width="41.73046875" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="9" max="9" width="16.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="30"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -2184,14 +2074,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="35">
-        <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
-        <v>4</v>
+      <c r="B2" s="33"/>
+      <c r="C2" s="36">
+        <f ca="1">COUNTIFS($B$9:$B$65494,"&lt;&gt;",$J$9:$J$65494,"&lt;&gt;論理削除")</f>
+        <v>3</v>
       </c>
       <c r="D2" s="18" t="str">
         <f>大中項目!B1</f>
@@ -2205,10 +2095,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="36"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="18" t="str">
         <f>大中項目!B2</f>
         <v>Ajax</v>
@@ -2221,7 +2111,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2232,33 +2122,33 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39"/>
-    </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="40" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
+    </row>
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="42"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="43"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2269,7 +2159,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -2298,118 +2188,88 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="157.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="17">
         <f t="shared" ref="B9:B11" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="185.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="185.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="190.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="190.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="19">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="409.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="19">
-        <f t="shared" ref="B12" ca="1" si="1">IF(A12&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B12)-1,COLUMN(B12),4))+1)</f>
-        <v>1</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2421,16 +2281,16 @@
     <mergeCell ref="A6:I6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="B9:B12 A10:B12">
+  <conditionalFormatting sqref="B9:B11 A10:B11">
     <cfRule type="expression" dxfId="2" priority="47">
       <formula>A9&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C12" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C11" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"正常,クライアントエラー,サーバーエラー"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I12" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I11" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Selenium:○,Seleniumu:△,Selenium:×,JUnit:○,JUnit:△,Junit:×,手動実行,机上"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2451,23 +2311,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="7" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="7" width="41.73046875" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="9" max="9" width="16.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="30"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -2487,12 +2347,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="35">
+      <c r="B2" s="33"/>
+      <c r="C2" s="36">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>5</v>
       </c>
@@ -2508,10 +2368,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="36"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="18" t="str">
         <f>大中項目!B2</f>
         <v>Ajax</v>
@@ -2524,7 +2384,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2535,33 +2395,33 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39"/>
-    </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="40" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
+    </row>
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="42"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="43"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2572,7 +2432,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -2601,148 +2461,148 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="156" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="156" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" s="17">
         <f t="shared" ref="B9:B13" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="F9" s="13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="159" customHeight="1" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="159" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="I10" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="155.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="153.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="168" customHeight="1" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="168" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="19">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2784,23 +2644,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="7" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="7" width="41.73046875" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="9" max="9" width="16.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="30"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -2820,12 +2680,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="35">
+      <c r="B2" s="33"/>
+      <c r="C2" s="36">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>2</v>
       </c>
@@ -2841,10 +2701,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="36"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="18" t="str">
         <f>大中項目!B2</f>
         <v>Ajax</v>
@@ -2857,7 +2717,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2868,33 +2728,33 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39"/>
-    </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="40" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
+    </row>
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="42"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="43"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2905,7 +2765,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -2934,62 +2794,62 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="141.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="17">
         <f t="shared" ref="B9:B10" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="I9" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="204" customHeight="1" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="204" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="19">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
